--- a/reports/一级子公司A_利润表_2025-09.xlsx
+++ b/reports/一级子公司A_利润表_2025-09.xlsx
@@ -2049,7 +2049,7 @@
         </is>
       </c>
       <c r="F3" s="13" t="n">
-        <v>179263280</v>
+        <v>183549405</v>
       </c>
       <c r="G3" s="13" t="n"/>
       <c r="I3" s="5" t="n"/>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="F4" s="14" t="n">
-        <v>174652632</v>
+        <v>174935192</v>
       </c>
       <c r="G4" s="14" t="n">
-        <v>1518777184</v>
+        <v>1519510697</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="F5" s="14" t="n">
-        <v>714551</v>
+        <v>712327</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>6196936</v>
+        <v>6190874</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="F6" s="14" t="n">
-        <v>620798</v>
+        <v>619363</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>5377387</v>
+        <v>5372949</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="F7" s="14" t="n">
-        <v>523298</v>
+        <v>526015</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>4554172</v>
+        <v>4554855</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2214,10 +2214,10 @@
         </is>
       </c>
       <c r="F8" s="14" t="n">
-        <v>482946</v>
+        <v>484813</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>4190960</v>
+        <v>4191874</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2247,10 +2247,10 @@
         </is>
       </c>
       <c r="F9" s="14" t="n">
-        <v>261020</v>
+        <v>263805</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>2276007</v>
+        <v>2278864</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="F10" s="14" t="n">
-        <v>209674</v>
+        <v>211110</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>1821500</v>
+        <v>1823424</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>176450993</v>
+        <v>180731972</v>
       </c>
       <c r="G11" s="13" t="n"/>
     </row>
@@ -2344,7 +2344,7 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>171840345</v>
+        <v>172117759</v>
       </c>
       <c r="G12" s="13" t="n"/>
     </row>
@@ -2375,10 +2375,10 @@
         </is>
       </c>
       <c r="F13" s="14" t="n">
-        <v>88577708</v>
+        <v>89008798</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>769347980</v>
+        <v>770385095</v>
       </c>
     </row>
     <row r="14" ht="20.25" customHeight="1">
@@ -2408,10 +2408,10 @@
         </is>
       </c>
       <c r="F14" s="14" t="n">
-        <v>1627739</v>
+        <v>1627426</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>14117015</v>
+        <v>14125274</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="F15" s="14" t="n">
-        <v>1474973</v>
+        <v>1465339</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>12757103</v>
+        <v>12751573</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2474,10 +2474,10 @@
         </is>
       </c>
       <c r="F16" s="14" t="n">
-        <v>78382435</v>
+        <v>78286277</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>682895578</v>
+        <v>682662852</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="F17" s="14" t="n">
-        <v>1689847</v>
+        <v>1671145</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>14586091</v>
+        <v>14563681</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2540,10 +2540,10 @@
         </is>
       </c>
       <c r="F18" s="14" t="n">
-        <v>734329</v>
+        <v>731587</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>6377022</v>
+        <v>6371744</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="F19" s="14" t="n">
-        <v>2638821</v>
+        <v>2619169</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>22790758</v>
+        <v>22760498</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="F20" s="14" t="n">
-        <v>1154519</v>
+        <v>1152877</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>10022652</v>
+        <v>10015254</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -2639,10 +2639,10 @@
         </is>
       </c>
       <c r="F21" s="14" t="n">
-        <v>4520781</v>
+        <v>4515654</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>39188111</v>
+        <v>39160838</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -2672,10 +2672,10 @@
         </is>
       </c>
       <c r="F22" s="14" t="n">
-        <v>89867</v>
+        <v>90219</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>809905</v>
+        <v>810167</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2705,10 +2705,10 @@
         </is>
       </c>
       <c r="F23" s="14" t="n">
-        <v>0</v>
+        <v>2404128</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>0</v>
+        <v>20779323</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2738,10 +2738,10 @@
         </is>
       </c>
       <c r="F24" s="14" t="n">
-        <v>0</v>
+        <v>1604212</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>0</v>
+        <v>13856443</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>119405396</v>
+        <v>128871323</v>
       </c>
       <c r="G25" s="13" t="n"/>
     </row>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>106704650</v>
+        <v>107477421</v>
       </c>
       <c r="G26" s="13" t="n"/>
     </row>
@@ -2833,10 +2833,10 @@
         </is>
       </c>
       <c r="F27" s="14" t="n">
-        <v>104496118</v>
+        <v>105270738</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>910307251</v>
+        <v>911599199</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="F28" s="14" t="n">
-        <v>2208532</v>
+        <v>2206683</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>19130192</v>
+        <v>19139361</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2899,10 +2899,10 @@
         </is>
       </c>
       <c r="F29" s="14" t="n">
-        <v>0</v>
+        <v>3983253</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>0</v>
+        <v>34620428</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="F30" s="14" t="n">
-        <v>0</v>
+        <v>1272218</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>0</v>
+        <v>11074734</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="F31" s="14" t="n">
-        <v>0</v>
+        <v>794126</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>0</v>
+        <v>6919665</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2998,10 +2998,10 @@
         </is>
       </c>
       <c r="F32" s="14" t="n">
-        <v>0</v>
+        <v>952557</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>0</v>
+        <v>8301975</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -3031,10 +3031,10 @@
         </is>
       </c>
       <c r="F33" s="14" t="n">
-        <v>0</v>
+        <v>714788</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>0</v>
+        <v>6226105</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="F34" s="14" t="n">
-        <v>0</v>
+        <v>477172</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>0</v>
+        <v>4151087</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -3097,10 +3097,10 @@
         </is>
       </c>
       <c r="F35" s="14" t="n">
-        <v>0</v>
+        <v>398421</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>0</v>
+        <v>3459982</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -3130,10 +3130,10 @@
         </is>
       </c>
       <c r="F36" s="14" t="n">
-        <v>1832168</v>
+        <v>1839010</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>15940298</v>
+        <v>15939180</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="F37" s="14" t="n">
-        <v>1419661</v>
+        <v>1421558</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>12302451</v>
+        <v>12300143</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -3196,10 +3196,10 @@
         </is>
       </c>
       <c r="F38" s="14" t="n">
-        <v>1149551</v>
+        <v>1160016</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>10016134</v>
+        <v>10025366</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3229,10 +3229,10 @@
         </is>
       </c>
       <c r="F39" s="14" t="n">
-        <v>8702347</v>
+        <v>8760223</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>75599359</v>
+        <v>75664900</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="F40" s="14" t="n">
-        <v>348537</v>
+        <v>369397</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>3147881</v>
+        <v>3191083</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="F41" s="14" t="n">
-        <v>668143</v>
+        <v>672721</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>6027022</v>
+        <v>6034809</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3328,10 +3328,10 @@
         </is>
       </c>
       <c r="F42" s="14" t="n">
-        <v>759411</v>
+        <v>672721</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>6837928</v>
+        <v>6034809</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -3361,10 +3361,10 @@
         </is>
       </c>
       <c r="F43" s="14" t="n">
-        <v>89789</v>
+        <v>90034</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>809667</v>
+        <v>810225</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="F44" s="14" t="n">
-        <v>0</v>
+        <v>341327</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>0</v>
+        <v>3077627</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3427,10 +3427,10 @@
         </is>
       </c>
       <c r="F45" s="14" t="n">
-        <v>0</v>
+        <v>695597</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>0</v>
+        <v>6056234</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3460,10 +3460,10 @@
         </is>
       </c>
       <c r="F46" s="14" t="n">
-        <v>0</v>
+        <v>226869</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>0</v>
+        <v>2050493</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="F47" s="14" t="n">
-        <v>0</v>
+        <v>170102</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>0</v>
+        <v>1537658</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="F48" s="14" t="n">
-        <v>0</v>
+        <v>283684</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>0</v>
+        <v>2562807</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -3559,10 +3559,10 @@
         </is>
       </c>
       <c r="F49" s="14" t="n">
-        <v>0</v>
+        <v>994339</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>0</v>
+        <v>8648283</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3592,10 +3592,10 @@
         </is>
       </c>
       <c r="F50" s="14" t="n">
-        <v>0</v>
+        <v>151823</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>0</v>
+        <v>1367455</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="F51" s="14" t="n">
-        <v>0</v>
+        <v>114119</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>0</v>
+        <v>1025957</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -3658,10 +3658,10 @@
         </is>
       </c>
       <c r="F52" s="14" t="n">
-        <v>0</v>
+        <v>190583</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>0</v>
+        <v>1710555</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="F53" s="14" t="n">
-        <v>0</v>
+        <v>133606</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>0</v>
+        <v>1197759</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3724,10 +3724,10 @@
         </is>
       </c>
       <c r="F54" s="14" t="n">
-        <v>0</v>
+        <v>95498</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>0</v>
+        <v>855710</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -3757,10 +3757,10 @@
         </is>
       </c>
       <c r="F55" s="14" t="n">
-        <v>0</v>
+        <v>76380</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>0</v>
+        <v>684602</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3790,10 +3790,10 @@
         </is>
       </c>
       <c r="F56" s="14" t="n">
-        <v>0</v>
+        <v>57221</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>0</v>
+        <v>513400</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3823,7 +3823,7 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>57045597</v>
+        <v>54272495</v>
       </c>
       <c r="G57" s="13" t="n"/>
     </row>
@@ -3854,7 +3854,7 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>66014433</v>
+        <v>60931487</v>
       </c>
       <c r="G58" s="13" t="n"/>
     </row>
@@ -3885,10 +3885,10 @@
         </is>
       </c>
       <c r="F59" s="14" t="n">
-        <v>0</v>
+        <v>398106</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>0</v>
+        <v>3461722</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3918,10 +3918,10 @@
         </is>
       </c>
       <c r="F60" s="14" t="n">
-        <v>0</v>
+        <v>94620</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>0</v>
+        <v>854561</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3951,10 +3951,10 @@
         </is>
       </c>
       <c r="F61" s="14" t="n">
-        <v>150232</v>
+        <v>149243</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>1350384</v>
+        <v>1348975</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3984,7 +3984,7 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>56895365</v>
+        <v>54521358</v>
       </c>
       <c r="G62" s="13" t="n"/>
     </row>
@@ -4015,10 +4015,10 @@
         </is>
       </c>
       <c r="F63" s="14" t="n">
-        <v>5301491</v>
+        <v>5276298</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>47711503</v>
+        <v>47659876</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>51593874</v>
+        <v>49245060</v>
       </c>
       <c r="G64" s="13" t="n"/>
     </row>
@@ -4108,7 +4108,7 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>51593874</v>
+        <v>49245060</v>
       </c>
       <c r="G66" s="13" t="n"/>
     </row>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>51593874</v>
+        <v>49245060</v>
       </c>
       <c r="G69" s="13" t="n"/>
     </row>
@@ -4410,7 +4410,7 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>51593874</v>
+        <v>49245060</v>
       </c>
       <c r="G76" s="13" t="n"/>
     </row>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>51593874</v>
+        <v>49245060</v>
       </c>
       <c r="G77" s="13" t="n"/>
     </row>
